--- a/tests/testdata/utilityInputs.xlsx
+++ b/tests/testdata/utilityInputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mathworks-my.sharepoint.com/personal/msulliva_mathworks_com/Documents/Desktop/Client Work/Work_2025/P16569_NewEcology/repo/tests/fasttestdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SankhanilGoswami\Documents\Github\mathworks\Retrocalc_new\tests\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{2F20EE78-A088-4269-9043-C782AC363BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21FB2046-68CE-49B1-9F61-034493F25B38}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF86E3E5-55CE-4B3D-8DF3-81E764E3274F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{987BBB44-C9C6-4B0C-8010-09F974866F2F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{987BBB44-C9C6-4B0C-8010-09F974866F2F}"/>
   </bookViews>
   <sheets>
     <sheet name="elecMeter1" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,6 @@
     <sheet name="waterMeter1" sheetId="2" r:id="rId6"/>
     <sheet name="propaneMeter1" sheetId="9" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="56">
   <si>
     <t>1, 2, or 3 years of data</t>
   </si>
@@ -161,9 +158,6 @@
     <t>IsCooking</t>
   </si>
   <si>
-    <t>IsClothesDryer</t>
-  </si>
-  <si>
     <t>Therms</t>
   </si>
   <si>
@@ -208,12 +202,22 @@
   <si>
     <t>IsCommonAreaClothesDryer</t>
   </si>
+  <si>
+    <t>IrrigationGals</t>
+  </si>
+  <si>
+    <t>CoolingTowerGals</t>
+  </si>
+  <si>
+    <t>OtherGals</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -256,7 +260,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -266,6 +270,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -300,7 +310,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -344,6 +354,17 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -351,6 +372,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -369,569 +391,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="upgrades_NuestraGuest"/>
-      <sheetName val="Info"/>
-      <sheetName val="annual tables"/>
-      <sheetName val="graphs"/>
-      <sheetName val="HEAsummaryTable"/>
-      <sheetName val="applInps"/>
-      <sheetName val="basicInps"/>
-      <sheetName val="gasInputs"/>
-      <sheetName val="gasAcct1"/>
-      <sheetName val="gasAcct2"/>
-      <sheetName val="elecInputs"/>
-      <sheetName val="elecInputs1"/>
-      <sheetName val="elecInputs2"/>
-      <sheetName val="waterInputs"/>
-      <sheetName val="waterInputs1"/>
-      <sheetName val="elec clean"/>
-      <sheetName val="gas clean"/>
-      <sheetName val="clean water"/>
-      <sheetName val="318-320 Dudley Street - Electri"/>
-      <sheetName val="318-320 Dudley Street - Gas #51"/>
-      <sheetName val="318-320 Dudley Street - Water #"/>
-      <sheetName val="histDDBos"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17">
-        <row r="3">
-          <cell r="A3">
-            <v>43686</v>
-          </cell>
-          <cell r="B3">
-            <v>43713</v>
-          </cell>
-          <cell r="C3">
-            <v>37777</v>
-          </cell>
-          <cell r="D3">
-            <v>723.32</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>43714</v>
-          </cell>
-          <cell r="B4">
-            <v>43734</v>
-          </cell>
-          <cell r="C4">
-            <v>13203</v>
-          </cell>
-          <cell r="D4">
-            <v>264.27999999999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>43735</v>
-          </cell>
-          <cell r="B5">
-            <v>43767</v>
-          </cell>
-          <cell r="C5">
-            <v>22666</v>
-          </cell>
-          <cell r="D5">
-            <v>434.06</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>43768</v>
-          </cell>
-          <cell r="B6">
-            <v>43794</v>
-          </cell>
-          <cell r="C6">
-            <v>22277</v>
-          </cell>
-          <cell r="D6">
-            <v>433.18</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>43795</v>
-          </cell>
-          <cell r="B7">
-            <v>43825</v>
-          </cell>
-          <cell r="C7">
-            <v>21686</v>
-          </cell>
-          <cell r="D7">
-            <v>417.01</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>43826</v>
-          </cell>
-          <cell r="B8">
-            <v>43856</v>
-          </cell>
-          <cell r="C8">
-            <v>35697</v>
-          </cell>
-          <cell r="D8">
-            <v>736.51</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>43857</v>
-          </cell>
-          <cell r="B9">
-            <v>43886</v>
-          </cell>
-          <cell r="C9">
-            <v>38076</v>
-          </cell>
-          <cell r="D9">
-            <v>799.49</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>43887</v>
-          </cell>
-          <cell r="B10">
-            <v>43915</v>
-          </cell>
-          <cell r="C10">
-            <v>24716</v>
-          </cell>
-          <cell r="D10">
-            <v>624.64</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>43916</v>
-          </cell>
-          <cell r="B11">
-            <v>43944</v>
-          </cell>
-          <cell r="C11">
-            <v>19644</v>
-          </cell>
-          <cell r="D11">
-            <v>406.87</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>43945</v>
-          </cell>
-          <cell r="B12">
-            <v>43976</v>
-          </cell>
-          <cell r="C12">
-            <v>21297</v>
-          </cell>
-          <cell r="D12">
-            <v>437.01</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>43977</v>
-          </cell>
-          <cell r="B13">
-            <v>44005</v>
-          </cell>
-          <cell r="C13">
-            <v>17804</v>
-          </cell>
-          <cell r="D13">
-            <v>369.25</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>44006</v>
-          </cell>
-          <cell r="B14">
-            <v>44035</v>
-          </cell>
-          <cell r="C14">
-            <v>26765</v>
-          </cell>
-          <cell r="D14">
-            <v>557.1</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>44036</v>
-          </cell>
-          <cell r="B15">
-            <v>44067</v>
-          </cell>
-          <cell r="C15">
-            <v>20489</v>
-          </cell>
-          <cell r="D15">
-            <v>421.58</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>44068</v>
-          </cell>
-          <cell r="B16">
-            <v>44097</v>
-          </cell>
-          <cell r="C16">
-            <v>21005</v>
-          </cell>
-          <cell r="D16">
-            <v>434.58</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>44098</v>
-          </cell>
-          <cell r="B17">
-            <v>44126</v>
-          </cell>
-          <cell r="C17">
-            <v>18776</v>
-          </cell>
-          <cell r="D17">
-            <v>387.99</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>44127</v>
-          </cell>
-          <cell r="B18">
-            <v>44157</v>
-          </cell>
-          <cell r="C18">
-            <v>24895</v>
-          </cell>
-          <cell r="D18">
-            <v>516.46</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>44158</v>
-          </cell>
-          <cell r="B19">
-            <v>44189</v>
-          </cell>
-          <cell r="C19">
-            <v>27177</v>
-          </cell>
-          <cell r="D19">
-            <v>563.01</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>44190</v>
-          </cell>
-          <cell r="B20">
-            <v>44222</v>
-          </cell>
-          <cell r="C20">
-            <v>25471</v>
-          </cell>
-          <cell r="D20">
-            <v>559.42999999999995</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>44223</v>
-          </cell>
-          <cell r="B21">
-            <v>44252</v>
-          </cell>
-          <cell r="C21">
-            <v>24357</v>
-          </cell>
-          <cell r="D21">
-            <v>677.08</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>44253</v>
-          </cell>
-          <cell r="B22">
-            <v>44279</v>
-          </cell>
-          <cell r="C22">
-            <v>22651</v>
-          </cell>
-          <cell r="D22">
-            <v>512.97</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>44280</v>
-          </cell>
-          <cell r="B23">
-            <v>44313</v>
-          </cell>
-          <cell r="C23">
-            <v>24693</v>
-          </cell>
-          <cell r="D23">
-            <v>550.41</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24">
-            <v>44314</v>
-          </cell>
-          <cell r="B24">
-            <v>44338</v>
-          </cell>
-          <cell r="C24">
-            <v>28142</v>
-          </cell>
-          <cell r="D24">
-            <v>644.28</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25">
-            <v>44339</v>
-          </cell>
-          <cell r="B25">
-            <v>44371</v>
-          </cell>
-          <cell r="C25">
-            <v>43918</v>
-          </cell>
-          <cell r="D25">
-            <v>1000.63</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>44372</v>
-          </cell>
-          <cell r="B26">
-            <v>44403</v>
-          </cell>
-          <cell r="C26">
-            <v>33214</v>
-          </cell>
-          <cell r="D26">
-            <v>751.51</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>44404</v>
-          </cell>
-          <cell r="B27">
-            <v>44433</v>
-          </cell>
-          <cell r="C27">
-            <v>12881</v>
-          </cell>
-          <cell r="D27">
-            <v>290.49</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>44434</v>
-          </cell>
-          <cell r="B28">
-            <v>44462</v>
-          </cell>
-          <cell r="C28">
-            <v>8805</v>
-          </cell>
-          <cell r="D28">
-            <v>201.45</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>44463</v>
-          </cell>
-          <cell r="B29">
-            <v>44494</v>
-          </cell>
-          <cell r="C29">
-            <v>15253</v>
-          </cell>
-          <cell r="D29">
-            <v>340.38</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>44495</v>
-          </cell>
-          <cell r="B30">
-            <v>44525</v>
-          </cell>
-          <cell r="C30">
-            <v>20040</v>
-          </cell>
-          <cell r="D30">
-            <v>447.38</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>44526</v>
-          </cell>
-          <cell r="B31">
-            <v>44556</v>
-          </cell>
-          <cell r="C31">
-            <v>19539</v>
-          </cell>
-          <cell r="D31">
-            <v>435.43</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>44557</v>
-          </cell>
-          <cell r="B32">
-            <v>44586</v>
-          </cell>
-          <cell r="C32">
-            <v>14041</v>
-          </cell>
-          <cell r="D32">
-            <v>324.22000000000003</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>44587</v>
-          </cell>
-          <cell r="B33">
-            <v>44616</v>
-          </cell>
-          <cell r="C33">
-            <v>16053</v>
-          </cell>
-          <cell r="D33">
-            <v>501.56</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>44617</v>
-          </cell>
-          <cell r="B34">
-            <v>44644</v>
-          </cell>
-          <cell r="C34">
-            <v>16816</v>
-          </cell>
-          <cell r="D34">
-            <v>392.4</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>44645</v>
-          </cell>
-          <cell r="B35">
-            <v>44676</v>
-          </cell>
-          <cell r="C35">
-            <v>17003</v>
-          </cell>
-          <cell r="D35">
-            <v>393.59</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36">
-            <v>44677</v>
-          </cell>
-          <cell r="B36">
-            <v>44706</v>
-          </cell>
-          <cell r="C36">
-            <v>28329</v>
-          </cell>
-          <cell r="D36">
-            <v>672.73</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37">
-            <v>44707</v>
-          </cell>
-          <cell r="B37">
-            <v>44738</v>
-          </cell>
-          <cell r="C37">
-            <v>33962</v>
-          </cell>
-          <cell r="D37">
-            <v>810.1</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38">
-            <v>44739</v>
-          </cell>
-          <cell r="B38">
-            <v>44767</v>
-          </cell>
-          <cell r="C38">
-            <v>20721</v>
-          </cell>
-          <cell r="D38">
-            <v>484.97</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1252,37 +711,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E317C88-E9D7-406A-A693-B210A089A6FB}">
   <dimension ref="A1:AE64"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.42578125" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="24.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.453125" customWidth="1"/>
+    <col min="8" max="8" width="11.7265625" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" customWidth="1"/>
-    <col min="11" max="12" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="11.453125" customWidth="1"/>
+    <col min="11" max="12" width="11.81640625" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" customWidth="1"/>
-    <col min="16" max="16" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" customWidth="1"/>
-    <col min="19" max="19" width="10.5703125" customWidth="1"/>
-    <col min="21" max="21" width="10.28515625" customWidth="1"/>
-    <col min="22" max="22" width="11.85546875" customWidth="1"/>
-    <col min="23" max="23" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.453125" customWidth="1"/>
+    <col min="15" max="15" width="11.26953125" customWidth="1"/>
+    <col min="16" max="16" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.54296875" customWidth="1"/>
+    <col min="19" max="19" width="10.54296875" customWidth="1"/>
+    <col min="21" max="21" width="10.26953125" customWidth="1"/>
+    <col min="22" max="22" width="11.81640625" customWidth="1"/>
+    <col min="23" max="23" width="12.453125" customWidth="1"/>
     <col min="24" max="24" width="12" customWidth="1"/>
-    <col min="25" max="25" width="12.85546875" customWidth="1"/>
-    <col min="26" max="26" width="10.85546875" customWidth="1"/>
+    <col min="25" max="25" width="12.81640625" customWidth="1"/>
+    <col min="26" max="26" width="10.81640625" customWidth="1"/>
     <col min="29" max="29" width="17" customWidth="1"/>
-    <col min="30" max="30" width="27.85546875" customWidth="1"/>
-    <col min="31" max="31" width="28.140625" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" customWidth="1"/>
+    <col min="30" max="30" width="27.81640625" customWidth="1"/>
+    <col min="31" max="31" width="28.1796875" customWidth="1"/>
+    <col min="32" max="32" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -1293,7 +752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -1304,7 +763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -1315,7 +774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -1326,7 +785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -1337,9 +796,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -1348,9 +807,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -1359,9 +818,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -1370,37 +829,37 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="B10" s="1">
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1">
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -1414,7 +873,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>43164</v>
       </c>
@@ -1428,7 +887,7 @@
         <v>1007.82</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>43195</v>
       </c>
@@ -1442,7 +901,7 @@
         <v>818.4</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>43226</v>
       </c>
@@ -1456,7 +915,7 @@
         <v>986.92</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>43257</v>
       </c>
@@ -1470,7 +929,7 @@
         <v>1173.48</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>43288</v>
       </c>
@@ -1484,7 +943,7 @@
         <v>1661.88</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>43319</v>
       </c>
@@ -1498,7 +957,7 @@
         <v>1913.56</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>43349</v>
       </c>
@@ -1512,7 +971,7 @@
         <v>1549.68</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>43380</v>
       </c>
@@ -1526,7 +985,7 @@
         <v>1288.0999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>43411</v>
       </c>
@@ -1540,7 +999,7 @@
         <v>907.94</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>43442</v>
       </c>
@@ -1554,7 +1013,7 @@
         <v>818.4</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>43473</v>
       </c>
@@ -1568,7 +1027,7 @@
         <v>949.3</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>43504</v>
       </c>
@@ -1582,7 +1041,7 @@
         <v>833.14</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>43533</v>
       </c>
@@ -1596,7 +1055,7 @@
         <v>789.36</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>43564</v>
       </c>
@@ -1610,7 +1069,7 @@
         <v>754.6</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>43594</v>
       </c>
@@ -1624,7 +1083,7 @@
         <v>784.3</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>43625</v>
       </c>
@@ -1638,7 +1097,7 @@
         <v>846.34</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>43655</v>
       </c>
@@ -1652,7 +1111,7 @@
         <v>1469.82</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>43686</v>
       </c>
@@ -1669,7 +1128,7 @@
       <c r="AD31" s="8"/>
       <c r="AE31" s="8"/>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>43717</v>
       </c>
@@ -1683,7 +1142,7 @@
         <v>1160.94</v>
       </c>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>43747</v>
       </c>
@@ -1699,7 +1158,7 @@
       <c r="AC33" s="8"/>
       <c r="AD33" s="8"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>43778</v>
       </c>
@@ -1713,7 +1172,7 @@
         <v>840.18</v>
       </c>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>43808</v>
       </c>
@@ -1728,7 +1187,7 @@
       </c>
       <c r="AC35" s="8"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>43839</v>
       </c>
@@ -1742,7 +1201,7 @@
         <v>911.02</v>
       </c>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>43870</v>
       </c>
@@ -1756,7 +1215,7 @@
         <v>733.26</v>
       </c>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>43899</v>
       </c>
@@ -1770,7 +1229,7 @@
         <v>786.06000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>43930</v>
       </c>
@@ -1784,7 +1243,7 @@
         <v>866.14</v>
       </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>43960</v>
       </c>
@@ -1798,7 +1257,7 @@
         <v>874.5</v>
       </c>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>43991</v>
       </c>
@@ -1812,7 +1271,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>44021</v>
       </c>
@@ -1826,7 +1285,7 @@
         <v>1593.46</v>
       </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>44052</v>
       </c>
@@ -1840,7 +1299,7 @@
         <v>1952.72</v>
       </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>44083</v>
       </c>
@@ -1854,7 +1313,7 @@
         <v>1499.74</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>44113</v>
       </c>
@@ -1868,7 +1327,7 @@
         <v>1004.96</v>
       </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>44144</v>
       </c>
@@ -1882,7 +1341,7 @@
         <v>897.16</v>
       </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>44174</v>
       </c>
@@ -1896,7 +1355,7 @@
         <v>1116.94</v>
       </c>
     </row>
-    <row r="48" spans="1:30" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:30" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A48" s="5">
         <v>44205</v>
       </c>
@@ -1911,7 +1370,7 @@
         <v>911.02</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A49" s="5">
         <v>44236</v>
       </c>
@@ -1926,25 +1385,25 @@
         <v>733.26</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="29" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="38"/>
+      <c r="C51" s="38"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>7</v>
       </c>
       <c r="B52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" t="s">
         <v>44</v>
       </c>
-      <c r="C52" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -1955,7 +1414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -1966,7 +1425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>10</v>
       </c>
@@ -1977,7 +1436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -1988,7 +1447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>12</v>
       </c>
@@ -1999,7 +1458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -2010,7 +1469,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>14</v>
       </c>
@@ -2021,7 +1480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>15</v>
       </c>
@@ -2032,7 +1491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>16</v>
       </c>
@@ -2043,7 +1502,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -2054,7 +1513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -2065,7 +1524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>19</v>
       </c>
@@ -2087,37 +1546,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2D6CF64-3829-49D4-94D7-5708A189ED0B}">
   <dimension ref="A1:AE64"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.42578125" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="24.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.453125" customWidth="1"/>
+    <col min="8" max="8" width="11.7265625" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" customWidth="1"/>
-    <col min="11" max="12" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="11.453125" customWidth="1"/>
+    <col min="11" max="12" width="11.81640625" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" customWidth="1"/>
-    <col min="16" max="16" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" customWidth="1"/>
-    <col min="19" max="19" width="10.5703125" customWidth="1"/>
-    <col min="21" max="21" width="10.28515625" customWidth="1"/>
-    <col min="22" max="22" width="11.85546875" customWidth="1"/>
-    <col min="23" max="23" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.453125" customWidth="1"/>
+    <col min="15" max="15" width="11.26953125" customWidth="1"/>
+    <col min="16" max="16" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.54296875" customWidth="1"/>
+    <col min="19" max="19" width="10.54296875" customWidth="1"/>
+    <col min="21" max="21" width="10.26953125" customWidth="1"/>
+    <col min="22" max="22" width="11.81640625" customWidth="1"/>
+    <col min="23" max="23" width="12.453125" customWidth="1"/>
     <col min="24" max="24" width="12" customWidth="1"/>
-    <col min="25" max="25" width="12.85546875" customWidth="1"/>
-    <col min="26" max="26" width="10.85546875" customWidth="1"/>
+    <col min="25" max="25" width="12.81640625" customWidth="1"/>
+    <col min="26" max="26" width="10.81640625" customWidth="1"/>
     <col min="29" max="29" width="17" customWidth="1"/>
-    <col min="30" max="30" width="27.85546875" customWidth="1"/>
-    <col min="31" max="31" width="28.140625" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" customWidth="1"/>
+    <col min="30" max="30" width="27.81640625" customWidth="1"/>
+    <col min="31" max="31" width="28.1796875" customWidth="1"/>
+    <col min="32" max="32" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -2128,7 +1587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -2139,7 +1598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -2150,7 +1609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -2161,7 +1620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -2172,9 +1631,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -2183,9 +1642,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -2194,9 +1653,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -2205,37 +1664,37 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="B10" s="1">
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1">
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -2249,7 +1708,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>43529</v>
       </c>
@@ -2264,7 +1723,7 @@
       </c>
       <c r="E14" s="22"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>43560</v>
       </c>
@@ -2279,7 +1738,7 @@
       </c>
       <c r="E15" s="22"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>43591</v>
       </c>
@@ -2294,7 +1753,7 @@
       </c>
       <c r="E16" s="22"/>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>43622</v>
       </c>
@@ -2309,7 +1768,7 @@
       </c>
       <c r="E17" s="22"/>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>43653</v>
       </c>
@@ -2324,7 +1783,7 @@
       </c>
       <c r="E18" s="22"/>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>43684</v>
       </c>
@@ -2339,7 +1798,7 @@
       </c>
       <c r="E19" s="22"/>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>43715</v>
       </c>
@@ -2354,7 +1813,7 @@
       </c>
       <c r="E20" s="22"/>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>43746</v>
       </c>
@@ -2369,7 +1828,7 @@
       </c>
       <c r="E21" s="22"/>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>43777</v>
       </c>
@@ -2384,7 +1843,7 @@
       </c>
       <c r="E22" s="22"/>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>43808</v>
       </c>
@@ -2399,7 +1858,7 @@
       </c>
       <c r="E23" s="22"/>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>43839</v>
       </c>
@@ -2414,7 +1873,7 @@
       </c>
       <c r="E24" s="22"/>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>43870</v>
       </c>
@@ -2429,7 +1888,7 @@
       </c>
       <c r="E25" s="22"/>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>43901</v>
       </c>
@@ -2444,7 +1903,7 @@
       </c>
       <c r="E26" s="22"/>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>43932</v>
       </c>
@@ -2459,7 +1918,7 @@
       </c>
       <c r="E27" s="22"/>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>43963</v>
       </c>
@@ -2474,7 +1933,7 @@
       </c>
       <c r="E28" s="22"/>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>43994</v>
       </c>
@@ -2489,7 +1948,7 @@
       </c>
       <c r="E29" s="22"/>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>44025</v>
       </c>
@@ -2504,7 +1963,7 @@
       </c>
       <c r="E30" s="22"/>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>44056</v>
       </c>
@@ -2522,7 +1981,7 @@
       <c r="AD31" s="8"/>
       <c r="AE31" s="8"/>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>44087</v>
       </c>
@@ -2537,7 +1996,7 @@
       </c>
       <c r="E32" s="22"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>44118</v>
       </c>
@@ -2554,7 +2013,7 @@
       <c r="AC33" s="8"/>
       <c r="AD33" s="8"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>44149</v>
       </c>
@@ -2569,7 +2028,7 @@
       </c>
       <c r="E34" s="22"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>44180</v>
       </c>
@@ -2585,7 +2044,7 @@
       <c r="E35" s="22"/>
       <c r="AC35" s="8"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>44211</v>
       </c>
@@ -2600,7 +2059,7 @@
       </c>
       <c r="E36" s="22"/>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>44242</v>
       </c>
@@ -2615,7 +2074,7 @@
       </c>
       <c r="E37" s="22"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>44273</v>
       </c>
@@ -2630,7 +2089,7 @@
       </c>
       <c r="E38" s="22"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>44304</v>
       </c>
@@ -2645,7 +2104,7 @@
       </c>
       <c r="E39" s="22"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>44335</v>
       </c>
@@ -2660,7 +2119,7 @@
       </c>
       <c r="E40" s="22"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>44366</v>
       </c>
@@ -2675,7 +2134,7 @@
       </c>
       <c r="E41" s="22"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>44397</v>
       </c>
@@ -2690,7 +2149,7 @@
       </c>
       <c r="E42" s="22"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>44428</v>
       </c>
@@ -2705,7 +2164,7 @@
       </c>
       <c r="E43" s="22"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>44459</v>
       </c>
@@ -2720,7 +2179,7 @@
       </c>
       <c r="E44" s="22"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>44490</v>
       </c>
@@ -2735,7 +2194,7 @@
       </c>
       <c r="E45" s="22"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>44521</v>
       </c>
@@ -2750,7 +2209,7 @@
       </c>
       <c r="E46" s="22"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>44552</v>
       </c>
@@ -2765,7 +2224,7 @@
       </c>
       <c r="E47" s="22"/>
     </row>
-    <row r="48" spans="1:30" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:30" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A48" s="5">
         <v>44583</v>
       </c>
@@ -2780,7 +2239,7 @@
       </c>
       <c r="E48" s="22"/>
     </row>
-    <row r="49" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A49" s="5">
         <v>44614</v>
       </c>
@@ -2795,25 +2254,25 @@
       </c>
       <c r="E49" s="22"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="29" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="38"/>
+      <c r="C51" s="38"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>7</v>
       </c>
       <c r="B52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" t="s">
         <v>44</v>
       </c>
-      <c r="C52" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -2824,7 +2283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -2835,7 +2294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>10</v>
       </c>
@@ -2846,7 +2305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -2857,7 +2316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>12</v>
       </c>
@@ -2868,7 +2327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -2879,7 +2338,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>14</v>
       </c>
@@ -2890,7 +2349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>15</v>
       </c>
@@ -2901,7 +2360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>16</v>
       </c>
@@ -2912,7 +2371,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -2923,7 +2382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -2934,7 +2393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>19</v>
       </c>
@@ -2956,12 +2415,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD95D2E9-5432-4277-BCBF-1F454F840368}">
   <dimension ref="A1:V50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.5703125" customWidth="1"/>
+    <col min="1" max="1" width="27.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -2972,18 +2431,18 @@
       <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -2994,16 +2453,16 @@
       <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="39"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -3014,16 +2473,16 @@
       <c r="D3" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -3038,9 +2497,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -3053,9 +2512,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -3068,9 +2527,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -3083,9 +2542,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -3098,9 +2557,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -3110,16 +2569,16 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="1">
         <v>0.8</v>
       </c>
       <c r="C10" s="18"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>24</v>
       </c>
@@ -3127,13 +2586,13 @@
         <v>25</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="13">
         <v>43282</v>
       </c>
@@ -3147,7 +2606,7 @@
         <v>107.08</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="14">
         <v>43312</v>
       </c>
@@ -3161,7 +2620,7 @@
         <v>110.89</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>43342</v>
       </c>
@@ -3175,7 +2634,7 @@
         <v>112.55</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="14">
         <v>43371</v>
       </c>
@@ -3189,7 +2648,7 @@
         <v>301.96000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="14">
         <v>43400</v>
       </c>
@@ -3203,7 +2662,7 @@
         <v>1015.29</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="14">
         <v>43433</v>
       </c>
@@ -3217,7 +2676,7 @@
         <v>999.8</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="14">
         <v>43463</v>
       </c>
@@ -3231,7 +2690,7 @@
         <v>1141.24</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="14">
         <v>43495</v>
       </c>
@@ -3245,7 +2704,7 @@
         <v>1018.4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="14">
         <v>43526</v>
       </c>
@@ -3259,7 +2718,7 @@
         <v>925.22</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="14">
         <v>43554</v>
       </c>
@@ -3273,7 +2732,7 @@
         <v>950.88</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="14">
         <v>43586</v>
       </c>
@@ -3287,7 +2746,7 @@
         <v>894.72</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="14">
         <v>43620</v>
       </c>
@@ -3301,7 +2760,7 @@
         <v>449.65999999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="14">
         <v>43645</v>
       </c>
@@ -3315,7 +2774,7 @@
         <v>139.99</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="14">
         <v>43678</v>
       </c>
@@ -3329,7 +2788,7 @@
         <v>112.43</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="14">
         <v>43709</v>
       </c>
@@ -3343,7 +2802,7 @@
         <v>455.55</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="14">
         <v>43739</v>
       </c>
@@ -3357,7 +2816,7 @@
         <v>885.83999999999992</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="14">
         <v>43769</v>
       </c>
@@ -3371,7 +2830,7 @@
         <v>875.68000000000006</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="14">
         <v>43801</v>
       </c>
@@ -3385,7 +2844,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="14">
         <v>43830</v>
       </c>
@@ -3399,7 +2858,7 @@
         <v>975.53</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="14">
         <v>43861</v>
       </c>
@@ -3413,7 +2872,7 @@
         <v>882.48</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="14">
         <v>43892</v>
       </c>
@@ -3427,7 +2886,7 @@
         <v>791.77355072463763</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="14">
         <v>43922</v>
       </c>
@@ -3441,7 +2900,7 @@
         <v>143.66</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="14">
         <v>43952</v>
       </c>
@@ -3455,7 +2914,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="14">
         <v>43983</v>
       </c>
@@ -3469,7 +2928,7 @@
         <v>761.82999999999993</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="14">
         <v>44014</v>
       </c>
@@ -3483,7 +2942,7 @@
         <v>992.63</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="14">
         <v>44043</v>
       </c>
@@ -3497,7 +2956,7 @@
         <v>964.19</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="14">
         <v>44075</v>
       </c>
@@ -3511,7 +2970,7 @@
         <v>1033.99</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="14">
         <v>44103</v>
       </c>
@@ -3525,7 +2984,7 @@
         <v>1044.3200000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="14">
         <v>44133</v>
       </c>
@@ -3539,7 +2998,7 @@
         <v>882.89</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="14">
         <v>44166</v>
       </c>
@@ -3553,7 +3012,7 @@
         <v>758.63</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="14">
         <v>44196</v>
       </c>
@@ -3567,7 +3026,7 @@
         <v>535.1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="14">
         <v>44226</v>
       </c>
@@ -3581,7 +3040,7 @@
         <v>260.89999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="14">
         <v>44257</v>
       </c>
@@ -3595,7 +3054,7 @@
         <v>208.63</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="14">
         <v>44288</v>
       </c>
@@ -3609,7 +3068,7 @@
         <v>123.81</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="14">
         <v>44317</v>
       </c>
@@ -3623,7 +3082,7 @@
         <v>125.85</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="14">
         <v>44349</v>
       </c>
@@ -3637,13 +3096,13 @@
         <v>129.61000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="19"/>
       <c r="B49" s="19"/>
       <c r="C49" s="20"/>
       <c r="D49" s="21"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="19"/>
       <c r="B50" s="19"/>
       <c r="C50" s="20"/>
@@ -3660,12 +3119,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E82F0780-5E39-4253-A926-E7DD55AF102E}">
   <dimension ref="A1:V50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -3676,18 +3135,18 @@
       <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -3698,16 +3157,16 @@
       <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="39"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -3718,16 +3177,16 @@
       <c r="D3" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -3742,18 +3201,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="18"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -3766,9 +3225,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -3781,9 +3240,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -3796,9 +3255,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -3808,16 +3267,16 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="1">
         <v>0.8</v>
       </c>
       <c r="C10" s="18"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>24</v>
       </c>
@@ -3825,13 +3284,13 @@
         <v>25</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="13">
         <v>43282</v>
       </c>
@@ -3845,7 +3304,7 @@
         <v>107.08</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="14">
         <v>43312</v>
       </c>
@@ -3859,7 +3318,7 @@
         <v>110.89</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>43342</v>
       </c>
@@ -3873,7 +3332,7 @@
         <v>112.55</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="14">
         <v>43371</v>
       </c>
@@ -3887,7 +3346,7 @@
         <v>301.96000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="14">
         <v>43400</v>
       </c>
@@ -3901,7 +3360,7 @@
         <v>1015.29</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="14">
         <v>43433</v>
       </c>
@@ -3915,7 +3374,7 @@
         <v>999.8</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="14">
         <v>43463</v>
       </c>
@@ -3929,7 +3388,7 @@
         <v>1141.24</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="14">
         <v>43495</v>
       </c>
@@ -3943,7 +3402,7 @@
         <v>1018.4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="14">
         <v>43526</v>
       </c>
@@ -3957,7 +3416,7 @@
         <v>925.22</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="14">
         <v>43554</v>
       </c>
@@ -3971,7 +3430,7 @@
         <v>950.88</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="14">
         <v>43586</v>
       </c>
@@ -3985,7 +3444,7 @@
         <v>894.72</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="14">
         <v>43620</v>
       </c>
@@ -3999,7 +3458,7 @@
         <v>449.65999999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="14">
         <v>43645</v>
       </c>
@@ -4013,7 +3472,7 @@
         <v>139.99</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="14">
         <v>43678</v>
       </c>
@@ -4027,7 +3486,7 @@
         <v>112.43</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="14">
         <v>43709</v>
       </c>
@@ -4041,7 +3500,7 @@
         <v>455.55</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="14">
         <v>43739</v>
       </c>
@@ -4055,7 +3514,7 @@
         <v>885.83999999999992</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="14">
         <v>43769</v>
       </c>
@@ -4069,7 +3528,7 @@
         <v>875.68000000000006</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="14">
         <v>43801</v>
       </c>
@@ -4083,7 +3542,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="14">
         <v>43830</v>
       </c>
@@ -4097,7 +3556,7 @@
         <v>975.53</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="14">
         <v>43861</v>
       </c>
@@ -4111,7 +3570,7 @@
         <v>882.48</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="14">
         <v>43892</v>
       </c>
@@ -4125,7 +3584,7 @@
         <v>791.77355072463763</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="14">
         <v>43922</v>
       </c>
@@ -4139,7 +3598,7 @@
         <v>143.66</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="14">
         <v>43952</v>
       </c>
@@ -4153,7 +3612,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="14">
         <v>43983</v>
       </c>
@@ -4167,7 +3626,7 @@
         <v>761.82999999999993</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="14">
         <v>44014</v>
       </c>
@@ -4181,7 +3640,7 @@
         <v>992.63</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="14">
         <v>44043</v>
       </c>
@@ -4195,7 +3654,7 @@
         <v>964.19</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="14">
         <v>44075</v>
       </c>
@@ -4209,7 +3668,7 @@
         <v>1033.99</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="14">
         <v>44103</v>
       </c>
@@ -4223,7 +3682,7 @@
         <v>1044.3200000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="14">
         <v>44133</v>
       </c>
@@ -4237,7 +3696,7 @@
         <v>882.89</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="14">
         <v>44166</v>
       </c>
@@ -4251,7 +3710,7 @@
         <v>758.63</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="14">
         <v>44196</v>
       </c>
@@ -4265,7 +3724,7 @@
         <v>535.1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="14">
         <v>44226</v>
       </c>
@@ -4279,7 +3738,7 @@
         <v>260.89999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="14">
         <v>44257</v>
       </c>
@@ -4293,7 +3752,7 @@
         <v>208.63</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="14">
         <v>44288</v>
       </c>
@@ -4307,7 +3766,7 @@
         <v>123.81</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="14">
         <v>44317</v>
       </c>
@@ -4321,7 +3780,7 @@
         <v>125.85</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="14">
         <v>44349</v>
       </c>
@@ -4335,13 +3794,13 @@
         <v>129.61000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="19"/>
       <c r="B49" s="19"/>
       <c r="C49" s="20"/>
       <c r="D49" s="21"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="19"/>
       <c r="B50" s="19"/>
       <c r="C50" s="20"/>
@@ -4358,13 +3817,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{059D451A-BF19-4DA7-B162-A3988E9A8428}">
   <dimension ref="A1:V47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -4375,18 +3834,18 @@
       <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -4397,16 +3856,16 @@
       <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="39"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -4417,18 +3876,18 @@
       <c r="D3" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -4441,9 +3900,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -4456,9 +3915,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -4468,21 +3927,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="1">
         <v>0.8</v>
       </c>
       <c r="C7" s="18"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="O8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
@@ -4490,16 +3949,16 @@
         <v>25</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="23">
         <v>44197</v>
       </c>
@@ -4513,7 +3972,7 @@
         <v>2112.2239999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="23">
         <v>44228</v>
       </c>
@@ -4527,7 +3986,7 @@
         <v>2182.85</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="23">
         <v>44256</v>
       </c>
@@ -4541,7 +4000,7 @@
         <v>2013.8839999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="23">
         <v>44287</v>
       </c>
@@ -4555,7 +4014,7 @@
         <v>865.09400000000005</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="23">
         <v>44317</v>
       </c>
@@ -4569,7 +4028,7 @@
         <v>493.78599999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="23">
         <v>44348</v>
       </c>
@@ -4583,7 +4042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="23">
         <v>44378</v>
       </c>
@@ -4597,7 +4056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="23">
         <v>44409</v>
       </c>
@@ -4611,7 +4070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="23">
         <v>44440</v>
       </c>
@@ -4625,7 +4084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="23">
         <v>44470</v>
       </c>
@@ -4639,7 +4098,7 @@
         <v>561.13400000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="23">
         <v>44501</v>
       </c>
@@ -4653,7 +4112,7 @@
         <v>1849.9839999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="23">
         <v>44531</v>
       </c>
@@ -4667,7 +4126,7 @@
         <v>3051.6093999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="23">
         <v>44562</v>
       </c>
@@ -4681,7 +4140,7 @@
         <v>4809.1260000000011</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="23">
         <v>44593</v>
       </c>
@@ -4695,7 +4154,7 @@
         <v>4095.777</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="23">
         <v>44621</v>
       </c>
@@ -4709,7 +4168,7 @@
         <v>3082.2680000000005</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="23">
         <v>44652</v>
       </c>
@@ -4723,7 +4182,7 @@
         <v>2280.2780000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="23">
         <v>44682</v>
       </c>
@@ -4737,7 +4196,7 @@
         <v>839.97900000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="23">
         <v>44713</v>
       </c>
@@ -4751,7 +4210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="23">
         <v>44743</v>
       </c>
@@ -4765,7 +4224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="23">
         <v>44774</v>
       </c>
@@ -4779,7 +4238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="23">
         <v>44805</v>
       </c>
@@ -4793,7 +4252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="23">
         <v>44835</v>
       </c>
@@ -4807,7 +4266,7 @@
         <v>632.2120000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="23">
         <v>44866</v>
       </c>
@@ -4821,7 +4280,7 @@
         <v>2400.8110000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="23">
         <v>44896</v>
       </c>
@@ -4835,7 +4294,7 @@
         <v>3710.2590000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="23">
         <v>44927</v>
       </c>
@@ -4849,7 +4308,7 @@
         <v>3160.8719999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="23">
         <v>44958</v>
       </c>
@@ -4863,7 +4322,7 @@
         <v>3357.7830000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="23">
         <v>44986</v>
       </c>
@@ -4877,7 +4336,7 @@
         <v>2492.4900000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="23">
         <v>45017</v>
       </c>
@@ -4891,7 +4350,7 @@
         <v>1382.2380000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="23">
         <v>45047</v>
       </c>
@@ -4905,7 +4364,7 @@
         <v>464.60699999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="23">
         <v>45078</v>
       </c>
@@ -4919,7 +4378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="23">
         <v>45108</v>
       </c>
@@ -4933,7 +4392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="23">
         <v>45139</v>
       </c>
@@ -4947,7 +4406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="23">
         <v>45170</v>
       </c>
@@ -4961,7 +4420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="23">
         <v>45200</v>
       </c>
@@ -4975,7 +4434,7 @@
         <v>1384.383</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="23">
         <v>45231</v>
       </c>
@@ -4989,7 +4448,7 @@
         <v>3181.893</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="23">
         <v>45261</v>
       </c>
@@ -5003,13 +4462,13 @@
         <v>2728.8690000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="19"/>
       <c r="B46" s="19"/>
       <c r="C46" s="20"/>
       <c r="D46" s="21"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="19"/>
       <c r="B47" s="19"/>
       <c r="C47" s="20"/>
@@ -5025,759 +4484,702 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{494481DB-71B1-407F-BC99-BF7AC3B41256}">
-  <dimension ref="A1:P44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P47"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" customWidth="1"/>
+    <col min="1" max="1" width="26.54296875" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" customWidth="1"/>
+    <col min="7" max="7" width="12.26953125" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" customWidth="1"/>
+    <col min="9" max="9" width="10.1796875" customWidth="1"/>
+    <col min="10" max="10" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.54296875" customWidth="1"/>
+    <col min="13" max="13" width="12.1796875" customWidth="1"/>
+    <col min="14" max="14" width="10.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B1" s="32">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="32"/>
+      <c r="D1" s="32" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B2" s="32">
+        <v>1</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="32">
         <v>0</v>
       </c>
-      <c r="D3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B4" s="32">
+        <v>1</v>
+      </c>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="32">
         <v>0</v>
       </c>
-      <c r="D5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="C5" s="32"/>
+      <c r="D5" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="32">
+        <v>0</v>
+      </c>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="32">
+        <v>1</v>
+      </c>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="32">
+        <v>1</v>
+      </c>
+      <c r="C9" s="36"/>
+      <c r="D9" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
-        <f>'[1]clean water'!A3</f>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="11">
         <v>43686</v>
       </c>
-      <c r="B9" s="11">
-        <f>'[1]clean water'!B3</f>
+      <c r="B12" s="11">
         <v>43713</v>
       </c>
-      <c r="C9" s="6">
-        <f>'[1]clean water'!C3</f>
+      <c r="C12" s="6">
         <v>37777</v>
       </c>
-      <c r="D9" s="7">
-        <f>'[1]clean water'!D3</f>
-        <v>723.32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <f>'[1]clean water'!A4</f>
+      <c r="D12" s="7">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="11">
         <v>43714</v>
       </c>
-      <c r="B10" s="11">
-        <f>'[1]clean water'!B4</f>
+      <c r="B13" s="11">
         <v>43734</v>
       </c>
-      <c r="C10" s="6">
-        <f>'[1]clean water'!C4</f>
+      <c r="C13" s="6">
         <v>13203</v>
       </c>
-      <c r="D10" s="7">
-        <f>'[1]clean water'!D4</f>
-        <v>264.27999999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
-        <f>'[1]clean water'!A5</f>
+      <c r="D13" s="7">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="11">
         <v>43735</v>
       </c>
-      <c r="B11" s="11">
-        <f>'[1]clean water'!B5</f>
+      <c r="B14" s="11">
         <v>43767</v>
       </c>
-      <c r="C11" s="6">
-        <f>'[1]clean water'!C5</f>
+      <c r="C14" s="6">
         <v>22666</v>
       </c>
-      <c r="D11" s="7">
-        <f>'[1]clean water'!D5</f>
-        <v>434.06</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
-        <f>'[1]clean water'!A6</f>
+      <c r="D14" s="7">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="11">
         <v>43768</v>
       </c>
-      <c r="B12" s="11">
-        <f>'[1]clean water'!B6</f>
+      <c r="B15" s="11">
         <v>43794</v>
       </c>
-      <c r="C12" s="6">
-        <f>'[1]clean water'!C6</f>
+      <c r="C15" s="6">
         <v>22277</v>
       </c>
-      <c r="D12" s="7">
-        <f>'[1]clean water'!D6</f>
-        <v>433.18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <f>'[1]clean water'!A7</f>
+      <c r="D15" s="7">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="11">
         <v>43795</v>
       </c>
-      <c r="B13" s="11">
-        <f>'[1]clean water'!B7</f>
+      <c r="B16" s="11">
         <v>43825</v>
       </c>
-      <c r="C13" s="6">
-        <f>'[1]clean water'!C7</f>
+      <c r="C16" s="6">
         <v>21686</v>
       </c>
-      <c r="D13" s="7">
-        <f>'[1]clean water'!D7</f>
-        <v>417.01</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <f>'[1]clean water'!A8</f>
+      <c r="D16" s="7">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A17" s="11">
         <v>43826</v>
       </c>
-      <c r="B14" s="11">
-        <f>'[1]clean water'!B8</f>
+      <c r="B17" s="11">
         <v>43856</v>
       </c>
-      <c r="C14" s="6">
-        <f>'[1]clean water'!C8</f>
+      <c r="C17" s="6">
         <v>35697</v>
       </c>
-      <c r="D14" s="7">
-        <f>'[1]clean water'!D8</f>
-        <v>736.51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
-        <f>'[1]clean water'!A9</f>
+      <c r="D17" s="7">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A18" s="11">
         <v>43857</v>
       </c>
-      <c r="B15" s="11">
-        <f>'[1]clean water'!B9</f>
+      <c r="B18" s="11">
         <v>43886</v>
       </c>
-      <c r="C15" s="6">
-        <f>'[1]clean water'!C9</f>
+      <c r="C18" s="6">
         <v>38076</v>
       </c>
-      <c r="D15" s="7">
-        <f>'[1]clean water'!D9</f>
-        <v>799.49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="11">
-        <f>'[1]clean water'!A10</f>
+      <c r="D18" s="7">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A19" s="11">
         <v>43887</v>
       </c>
-      <c r="B16" s="11">
-        <f>'[1]clean water'!B10</f>
+      <c r="B19" s="11">
         <v>43915</v>
       </c>
-      <c r="C16" s="6">
-        <f>'[1]clean water'!C10</f>
+      <c r="C19" s="6">
         <v>24716</v>
       </c>
-      <c r="D16" s="7">
-        <f>'[1]clean water'!D10</f>
-        <v>624.64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="11">
-        <f>'[1]clean water'!A11</f>
+      <c r="D19" s="7">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A20" s="11">
         <v>43916</v>
       </c>
-      <c r="B17" s="11">
-        <f>'[1]clean water'!B11</f>
+      <c r="B20" s="11">
         <v>43944</v>
       </c>
-      <c r="C17" s="6">
-        <f>'[1]clean water'!C11</f>
+      <c r="C20" s="6">
         <v>19644</v>
       </c>
-      <c r="D17" s="7">
-        <f>'[1]clean water'!D11</f>
-        <v>406.87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
-        <f>'[1]clean water'!A12</f>
+      <c r="D20" s="7">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A21" s="11">
         <v>43945</v>
       </c>
-      <c r="B18" s="11">
-        <f>'[1]clean water'!B12</f>
+      <c r="B21" s="11">
         <v>43976</v>
       </c>
-      <c r="C18" s="6">
-        <f>'[1]clean water'!C12</f>
+      <c r="C21" s="6">
         <v>21297</v>
       </c>
-      <c r="D18" s="7">
-        <f>'[1]clean water'!D12</f>
-        <v>437.01</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="11">
-        <f>'[1]clean water'!A13</f>
+      <c r="D21" s="7">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A22" s="11">
         <v>43977</v>
       </c>
-      <c r="B19" s="11">
-        <f>'[1]clean water'!B13</f>
+      <c r="B22" s="11">
         <v>44005</v>
       </c>
-      <c r="C19" s="6">
-        <f>'[1]clean water'!C13</f>
+      <c r="C22" s="6">
         <v>17804</v>
       </c>
-      <c r="D19" s="7">
-        <f>'[1]clean water'!D13</f>
-        <v>369.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="11">
-        <f>'[1]clean water'!A14</f>
+      <c r="D22" s="7">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A23" s="11">
         <v>44006</v>
       </c>
-      <c r="B20" s="11">
-        <f>'[1]clean water'!B14</f>
+      <c r="B23" s="11">
         <v>44035</v>
       </c>
-      <c r="C20" s="6">
-        <f>'[1]clean water'!C14</f>
+      <c r="C23" s="6">
         <v>26765</v>
       </c>
-      <c r="D20" s="7">
-        <f>'[1]clean water'!D14</f>
-        <v>557.1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
-        <f>'[1]clean water'!A15</f>
+      <c r="D23" s="7">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A24" s="11">
         <v>44036</v>
       </c>
-      <c r="B21" s="11">
-        <f>'[1]clean water'!B15</f>
+      <c r="B24" s="11">
         <v>44067</v>
       </c>
-      <c r="C21" s="6">
-        <f>'[1]clean water'!C15</f>
+      <c r="C24" s="6">
         <v>20489</v>
       </c>
-      <c r="D21" s="7">
-        <f>'[1]clean water'!D15</f>
-        <v>421.58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="11">
-        <f>'[1]clean water'!A16</f>
+      <c r="D24" s="7">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A25" s="11">
         <v>44068</v>
       </c>
-      <c r="B22" s="11">
-        <f>'[1]clean water'!B16</f>
+      <c r="B25" s="11">
         <v>44097</v>
       </c>
-      <c r="C22" s="6">
-        <f>'[1]clean water'!C16</f>
+      <c r="C25" s="6">
         <v>21005</v>
       </c>
-      <c r="D22" s="7">
-        <f>'[1]clean water'!D16</f>
-        <v>434.58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="11">
-        <f>'[1]clean water'!A17</f>
+      <c r="D25" s="7">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A26" s="11">
         <v>44098</v>
       </c>
-      <c r="B23" s="11">
-        <f>'[1]clean water'!B17</f>
+      <c r="B26" s="11">
         <v>44126</v>
       </c>
-      <c r="C23" s="6">
-        <f>'[1]clean water'!C17</f>
+      <c r="C26" s="6">
         <v>18776</v>
       </c>
-      <c r="D23" s="7">
-        <f>'[1]clean water'!D17</f>
-        <v>387.99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="11">
-        <f>'[1]clean water'!A18</f>
+      <c r="D26" s="7">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A27" s="11">
         <v>44127</v>
       </c>
-      <c r="B24" s="11">
-        <f>'[1]clean water'!B18</f>
+      <c r="B27" s="11">
         <v>44157</v>
       </c>
-      <c r="C24" s="6">
-        <f>'[1]clean water'!C18</f>
+      <c r="C27" s="6">
         <v>24895</v>
       </c>
-      <c r="D24" s="7">
-        <f>'[1]clean water'!D18</f>
-        <v>516.46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="11">
-        <f>'[1]clean water'!A19</f>
+      <c r="D27" s="7">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A28" s="11">
         <v>44158</v>
       </c>
-      <c r="B25" s="11">
-        <f>'[1]clean water'!B19</f>
+      <c r="B28" s="11">
         <v>44189</v>
       </c>
-      <c r="C25" s="6">
-        <f>'[1]clean water'!C19</f>
+      <c r="C28" s="6">
         <v>27177</v>
       </c>
-      <c r="D25" s="7">
-        <f>'[1]clean water'!D19</f>
-        <v>563.01</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
-        <f>'[1]clean water'!A20</f>
+      <c r="D28" s="7">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A29" s="11">
         <v>44190</v>
       </c>
-      <c r="B26" s="11">
-        <f>'[1]clean water'!B20</f>
+      <c r="B29" s="11">
         <v>44222</v>
       </c>
-      <c r="C26" s="6">
-        <f>'[1]clean water'!C20</f>
+      <c r="C29" s="6">
         <v>25471</v>
       </c>
-      <c r="D26" s="7">
-        <f>'[1]clean water'!D20</f>
-        <v>559.42999999999995</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
-        <f>'[1]clean water'!A21</f>
+      <c r="D29" s="7">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A30" s="11">
         <v>44223</v>
       </c>
-      <c r="B27" s="11">
-        <f>'[1]clean water'!B21</f>
+      <c r="B30" s="11">
         <v>44252</v>
       </c>
-      <c r="C27" s="6">
-        <f>'[1]clean water'!C21</f>
+      <c r="C30" s="6">
         <v>24357</v>
       </c>
-      <c r="D27" s="7">
-        <f>'[1]clean water'!D21</f>
-        <v>677.08</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="11">
-        <f>'[1]clean water'!A22</f>
+      <c r="D30" s="7">
+        <v>677</v>
+      </c>
+      <c r="P30" s="12"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A31" s="11">
         <v>44253</v>
       </c>
-      <c r="B28" s="11">
-        <f>'[1]clean water'!B22</f>
+      <c r="B31" s="11">
         <v>44279</v>
       </c>
-      <c r="C28" s="6">
-        <f>'[1]clean water'!C22</f>
+      <c r="C31" s="6">
         <v>22651</v>
       </c>
-      <c r="D28" s="7">
-        <f>'[1]clean water'!D22</f>
-        <v>512.97</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="11">
-        <f>'[1]clean water'!A23</f>
+      <c r="D31" s="7">
+        <v>513</v>
+      </c>
+      <c r="P31" s="12"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A32" s="11">
         <v>44280</v>
       </c>
-      <c r="B29" s="11">
-        <f>'[1]clean water'!B23</f>
+      <c r="B32" s="11">
         <v>44313</v>
       </c>
-      <c r="C29" s="6">
-        <f>'[1]clean water'!C23</f>
+      <c r="C32" s="6">
         <v>24693</v>
       </c>
-      <c r="D29" s="7">
-        <f>'[1]clean water'!D23</f>
-        <v>550.41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="11">
-        <f>'[1]clean water'!A24</f>
+      <c r="D32" s="7">
+        <v>550</v>
+      </c>
+      <c r="P32" s="12"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A33" s="11">
         <v>44314</v>
       </c>
-      <c r="B30" s="11">
-        <f>'[1]clean water'!B24</f>
+      <c r="B33" s="11">
         <v>44338</v>
       </c>
-      <c r="C30" s="6">
-        <f>'[1]clean water'!C24</f>
+      <c r="C33" s="6">
         <v>28142</v>
       </c>
-      <c r="D30" s="7">
-        <f>'[1]clean water'!D24</f>
-        <v>644.28</v>
-      </c>
-      <c r="P30" s="12"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="11">
-        <f>'[1]clean water'!A25</f>
+      <c r="D33" s="7">
+        <v>644</v>
+      </c>
+      <c r="P33" s="12"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A34" s="11">
         <v>44339</v>
       </c>
-      <c r="B31" s="11">
-        <f>'[1]clean water'!B25</f>
+      <c r="B34" s="11">
         <v>44371</v>
       </c>
-      <c r="C31" s="6">
-        <f>'[1]clean water'!C25</f>
+      <c r="C34" s="6">
         <v>43918</v>
       </c>
-      <c r="D31" s="7">
-        <f>'[1]clean water'!D25</f>
-        <v>1000.63</v>
-      </c>
-      <c r="P31" s="12"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="11">
-        <f>'[1]clean water'!A26</f>
+      <c r="D34" s="7">
+        <v>1001</v>
+      </c>
+      <c r="P34" s="12"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A35" s="11">
         <v>44372</v>
       </c>
-      <c r="B32" s="11">
-        <f>'[1]clean water'!B26</f>
+      <c r="B35" s="11">
         <v>44403</v>
       </c>
-      <c r="C32" s="6">
-        <f>'[1]clean water'!C26</f>
+      <c r="C35" s="6">
         <v>33214</v>
       </c>
-      <c r="D32" s="7">
-        <f>'[1]clean water'!D26</f>
-        <v>751.51</v>
-      </c>
-      <c r="P32" s="12"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
-        <f>'[1]clean water'!A27</f>
+      <c r="D35" s="7">
+        <v>752</v>
+      </c>
+      <c r="P35" s="12"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A36" s="11">
         <v>44404</v>
       </c>
-      <c r="B33" s="11">
-        <f>'[1]clean water'!B27</f>
+      <c r="B36" s="11">
         <v>44433</v>
       </c>
-      <c r="C33" s="6">
-        <f>'[1]clean water'!C27</f>
+      <c r="C36" s="6">
         <v>12881</v>
       </c>
-      <c r="D33" s="7">
-        <f>'[1]clean water'!D27</f>
-        <v>290.49</v>
-      </c>
-      <c r="P33" s="12"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="11">
-        <f>'[1]clean water'!A28</f>
+      <c r="D36" s="7">
+        <v>290</v>
+      </c>
+      <c r="P36" s="12"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A37" s="11">
         <v>44434</v>
       </c>
-      <c r="B34" s="11">
-        <f>'[1]clean water'!B28</f>
+      <c r="B37" s="11">
         <v>44462</v>
       </c>
-      <c r="C34" s="6">
-        <f>'[1]clean water'!C28</f>
+      <c r="C37" s="6">
         <v>8805</v>
       </c>
-      <c r="D34" s="7">
-        <f>'[1]clean water'!D28</f>
-        <v>201.45</v>
-      </c>
-      <c r="P34" s="12"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="11">
-        <f>'[1]clean water'!A29</f>
+      <c r="D37" s="7">
+        <v>201</v>
+      </c>
+      <c r="P37" s="12"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A38" s="11">
         <v>44463</v>
       </c>
-      <c r="B35" s="11">
-        <f>'[1]clean water'!B29</f>
+      <c r="B38" s="11">
         <v>44494</v>
       </c>
-      <c r="C35" s="6">
-        <f>'[1]clean water'!C29</f>
+      <c r="C38" s="6">
         <v>15253</v>
       </c>
-      <c r="D35" s="7">
-        <f>'[1]clean water'!D29</f>
-        <v>340.38</v>
-      </c>
-      <c r="P35" s="12"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="11">
-        <f>'[1]clean water'!A30</f>
+      <c r="D38" s="7">
+        <v>340</v>
+      </c>
+      <c r="P38" s="12"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A39" s="11">
         <v>44495</v>
       </c>
-      <c r="B36" s="11">
-        <f>'[1]clean water'!B30</f>
+      <c r="B39" s="11">
         <v>44525</v>
       </c>
-      <c r="C36" s="6">
-        <f>'[1]clean water'!C30</f>
+      <c r="C39" s="6">
         <v>20040</v>
       </c>
-      <c r="D36" s="7">
-        <f>'[1]clean water'!D30</f>
-        <v>447.38</v>
-      </c>
-      <c r="P36" s="12"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="11">
-        <f>'[1]clean water'!A31</f>
+      <c r="D39" s="7">
+        <v>447</v>
+      </c>
+      <c r="P39" s="12"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A40" s="11">
         <v>44526</v>
       </c>
-      <c r="B37" s="11">
-        <f>'[1]clean water'!B31</f>
+      <c r="B40" s="11">
         <v>44556</v>
       </c>
-      <c r="C37" s="6">
-        <f>'[1]clean water'!C31</f>
+      <c r="C40" s="6">
         <v>19539</v>
       </c>
-      <c r="D37" s="7">
-        <f>'[1]clean water'!D31</f>
-        <v>435.43</v>
-      </c>
-      <c r="P37" s="12"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="11">
-        <f>'[1]clean water'!A32</f>
+      <c r="D40" s="7">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A41" s="11">
         <v>44557</v>
       </c>
-      <c r="B38" s="11">
-        <f>'[1]clean water'!B32</f>
+      <c r="B41" s="11">
         <v>44586</v>
       </c>
-      <c r="C38" s="6">
-        <f>'[1]clean water'!C32</f>
+      <c r="C41" s="6">
         <v>14041</v>
       </c>
-      <c r="D38" s="7">
-        <f>'[1]clean water'!D32</f>
-        <v>324.22000000000003</v>
-      </c>
-      <c r="P38" s="12"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
-        <f>'[1]clean water'!A33</f>
+      <c r="D41" s="7">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A42" s="11">
         <v>44587</v>
       </c>
-      <c r="B39" s="11">
-        <f>'[1]clean water'!B33</f>
+      <c r="B42" s="11">
         <v>44616</v>
       </c>
-      <c r="C39" s="6">
-        <f>'[1]clean water'!C33</f>
+      <c r="C42" s="6">
         <v>16053</v>
       </c>
-      <c r="D39" s="7">
-        <f>'[1]clean water'!D33</f>
-        <v>501.56</v>
-      </c>
-      <c r="P39" s="12"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="11">
-        <f>'[1]clean water'!A34</f>
+      <c r="D42" s="7">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A43" s="11">
         <v>44617</v>
       </c>
-      <c r="B40" s="11">
-        <f>'[1]clean water'!B34</f>
+      <c r="B43" s="11">
         <v>44644</v>
       </c>
-      <c r="C40" s="6">
-        <f>'[1]clean water'!C34</f>
+      <c r="C43" s="6">
         <v>16816</v>
       </c>
-      <c r="D40" s="7">
-        <f>'[1]clean water'!D34</f>
-        <v>392.4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="11">
-        <f>'[1]clean water'!A35</f>
+      <c r="D43" s="7">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A44" s="11">
         <v>44645</v>
       </c>
-      <c r="B41" s="11">
-        <f>'[1]clean water'!B35</f>
+      <c r="B44" s="11">
         <v>44676</v>
       </c>
-      <c r="C41" s="6">
-        <f>'[1]clean water'!C35</f>
+      <c r="C44" s="6">
         <v>17003</v>
       </c>
-      <c r="D41" s="7">
-        <f>'[1]clean water'!D35</f>
-        <v>393.59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="11">
-        <f>'[1]clean water'!A36</f>
+      <c r="D44" s="7">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A45" s="29">
         <v>44677</v>
       </c>
-      <c r="B42" s="11">
-        <f>'[1]clean water'!B36</f>
+      <c r="B45" s="29">
         <v>44706</v>
       </c>
-      <c r="C42" s="6">
-        <f>'[1]clean water'!C36</f>
+      <c r="C45" s="30">
         <v>28329</v>
       </c>
-      <c r="D42" s="7">
-        <f>'[1]clean water'!D36</f>
-        <v>672.73</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="11">
-        <f>'[1]clean water'!A37</f>
+      <c r="D45" s="31">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A46" s="29">
         <v>44707</v>
       </c>
-      <c r="B43" s="11">
-        <f>'[1]clean water'!B37</f>
+      <c r="B46" s="29">
         <v>44738</v>
       </c>
-      <c r="C43" s="6">
-        <f>'[1]clean water'!C37</f>
+      <c r="C46" s="30">
         <v>33962</v>
       </c>
-      <c r="D43" s="7">
-        <f>'[1]clean water'!D37</f>
-        <v>810.1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="11">
-        <f>'[1]clean water'!A38</f>
+      <c r="D46" s="31">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A47" s="29">
         <v>44739</v>
       </c>
-      <c r="B44" s="11">
-        <f>'[1]clean water'!B38</f>
+      <c r="B47" s="29">
         <v>44767</v>
       </c>
-      <c r="C44" s="6">
-        <f>'[1]clean water'!C38</f>
+      <c r="C47" s="30">
         <v>20721</v>
       </c>
-      <c r="D44" s="7">
-        <f>'[1]clean water'!D38</f>
-        <v>484.97</v>
+      <c r="D47" s="31">
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -5787,14 +5189,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AC73AD8-461D-4BBE-9A9E-7CA9D89D9809}">
-  <dimension ref="A1:V49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V50"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -5805,18 +5207,18 @@
       <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -5827,16 +5229,16 @@
       <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="39"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -5847,16 +5249,16 @@
       <c r="D3" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -5871,9 +5273,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>38</v>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A5" s="41" t="s">
+        <v>51</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
@@ -5886,617 +5288,626 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A6" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0</v>
+      </c>
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="18"/>
-      <c r="D6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="18"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="1">
-        <v>1</v>
-      </c>
-      <c r="C7" s="18"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-      <c r="C8" s="18"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="18"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C10" s="18"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O11" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="C9" s="18"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="O10" t="s">
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A13" s="25">
         <v>43111</v>
       </c>
-      <c r="B12" s="23">
-        <f>$A13-1</f>
+      <c r="B13" s="23">
+        <f>$A14-1</f>
         <v>43129</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C13" s="27">
         <v>23.8</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D13" s="28">
         <v>69.5</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A14" s="25">
         <v>43130</v>
       </c>
-      <c r="B13" s="23">
-        <f t="shared" ref="B13:B46" si="0">$A14-1</f>
+      <c r="B14" s="23">
+        <f t="shared" ref="B14:B47" si="0">$A15-1</f>
         <v>43150</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C14" s="27">
         <v>14.8</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D14" s="28">
         <v>46.18</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A15" s="25">
         <v>43151</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <f t="shared" si="0"/>
         <v>43170</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C15" s="27">
         <v>24.8</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D15" s="28">
         <v>77.38</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A16" s="25">
         <v>43171</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <f t="shared" si="0"/>
         <v>43191</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C16" s="27">
         <v>32.1</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D16" s="28">
         <v>100.15</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="25">
         <v>43192</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <f t="shared" si="0"/>
         <v>43214</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C17" s="27">
         <v>30.2</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D17" s="28">
         <v>94.22</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="25">
         <v>43215</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <f t="shared" si="0"/>
         <v>43235</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C18" s="27">
         <v>27.9</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D18" s="28">
         <v>87.05</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="25">
         <v>43236</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <f t="shared" si="0"/>
         <v>43256</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C19" s="27">
         <v>26.5</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D19" s="28">
         <v>82.68</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="25">
         <v>43257</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <f t="shared" si="0"/>
         <v>43277</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C20" s="27">
         <v>20.5</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D20" s="28">
         <v>63.96</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="25">
         <v>43278</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <f t="shared" si="0"/>
         <v>43298</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C21" s="27">
         <v>23.1</v>
       </c>
-      <c r="D20" s="28">
+      <c r="D21" s="28">
         <v>68.38</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="25">
         <v>43299</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <f t="shared" si="0"/>
         <v>43320</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C22" s="27">
         <v>21.4</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D22" s="28">
         <v>63.34</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="25">
         <v>43321</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <f t="shared" si="0"/>
         <v>43340</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C23" s="27">
         <v>21.4</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D23" s="28">
         <v>63.34</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="25">
         <v>43341</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <f t="shared" si="0"/>
         <v>43361</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C24" s="27">
         <v>19.7</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D24" s="28">
         <v>56.34</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="25">
         <v>43362</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <f t="shared" si="0"/>
         <v>43382</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C25" s="27">
         <v>35.4</v>
       </c>
-      <c r="D24" s="28">
+      <c r="D25" s="28">
         <v>101.24</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="25">
         <v>43383</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <f t="shared" si="0"/>
         <v>43402</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C26" s="27">
         <v>24.4</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D26" s="28">
         <v>72.22</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="25">
         <v>43403</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <f t="shared" si="0"/>
         <v>43423</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C27" s="27">
         <v>38.1</v>
       </c>
-      <c r="D26" s="28">
+      <c r="D27" s="28">
         <v>112.78</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="25">
         <v>43424</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <f t="shared" si="0"/>
         <v>43450</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C28" s="27">
         <v>37.299999999999997</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D28" s="28">
         <v>110.41</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="25">
         <v>43451</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <f t="shared" si="0"/>
         <v>43473</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C29" s="27">
         <v>42.3</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D29" s="28">
         <v>125.21</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="25">
         <v>43474</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <f t="shared" si="0"/>
         <v>43496</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C30" s="27">
         <v>40.9</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D30" s="28">
         <v>116.97</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="25">
         <v>43497</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <f t="shared" si="0"/>
         <v>43515</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C31" s="27">
         <v>38</v>
       </c>
-      <c r="D30" s="28">
+      <c r="D31" s="28">
         <v>108.68</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="25">
         <v>43516</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <f t="shared" si="0"/>
         <v>43537</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C32" s="27">
         <v>29</v>
       </c>
-      <c r="D31" s="28">
+      <c r="D32" s="28">
         <v>82.94</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="25">
         <v>43538</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <f t="shared" si="0"/>
         <v>43556</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C33" s="27">
         <v>40.299999999999997</v>
       </c>
-      <c r="D32" s="28">
+      <c r="D33" s="28">
         <v>115.26</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="25">
         <v>43557</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <f t="shared" si="0"/>
         <v>43578</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C34" s="27">
         <v>23.1</v>
       </c>
-      <c r="D33" s="28">
+      <c r="D34" s="28">
         <v>66.069999999999993</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="25">
         <v>43579</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <f t="shared" si="0"/>
         <v>43599</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C35" s="27">
         <v>34</v>
       </c>
-      <c r="D34" s="28">
+      <c r="D35" s="28">
         <v>97.24</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="25">
         <v>43600</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <f t="shared" si="0"/>
         <v>43620</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C36" s="27">
         <v>38.799999999999997</v>
       </c>
-      <c r="D35" s="28">
+      <c r="D36" s="28">
         <v>110.97</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="25">
         <v>43621</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <f t="shared" si="0"/>
         <v>43640</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C37" s="27">
         <v>20.8</v>
       </c>
-      <c r="D36" s="28">
+      <c r="D37" s="28">
         <v>59.49</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="25">
         <v>43641</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <f t="shared" si="0"/>
         <v>43662</v>
       </c>
-      <c r="C37" s="27">
+      <c r="C38" s="27">
         <v>32.4</v>
       </c>
-      <c r="D37" s="28">
+      <c r="D38" s="28">
         <v>92.66</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="25">
         <v>43663</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <f t="shared" si="0"/>
         <v>43682</v>
       </c>
-      <c r="C38" s="27">
+      <c r="C39" s="27">
         <v>16.7</v>
       </c>
-      <c r="D38" s="28">
+      <c r="D39" s="28">
         <v>47.76</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="25">
         <v>43683</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <f t="shared" si="0"/>
         <v>43703</v>
       </c>
-      <c r="C39" s="27">
+      <c r="C40" s="27">
         <v>31.7</v>
       </c>
-      <c r="D39" s="28">
+      <c r="D40" s="28">
         <v>90.66</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="25">
         <v>43704</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <f t="shared" si="0"/>
         <v>43725</v>
       </c>
-      <c r="C40" s="27">
+      <c r="C41" s="27">
         <v>33</v>
       </c>
-      <c r="D40" s="28">
+      <c r="D41" s="28">
         <v>94.38</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="25">
         <v>43726</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <f t="shared" si="0"/>
         <v>43746</v>
       </c>
-      <c r="C41" s="27">
+      <c r="C42" s="27">
         <v>33</v>
       </c>
-      <c r="D41" s="28">
+      <c r="D42" s="28">
         <v>94.38</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="25">
         <v>43747</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <f t="shared" si="0"/>
         <v>43765</v>
       </c>
-      <c r="C42" s="27">
+      <c r="C43" s="27">
         <v>31.6</v>
       </c>
-      <c r="D42" s="28">
+      <c r="D43" s="28">
         <v>90.38</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="25">
         <v>43766</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <f t="shared" si="0"/>
         <v>43786</v>
       </c>
-      <c r="C43" s="27">
+      <c r="C44" s="27">
         <v>20.9</v>
       </c>
-      <c r="D43" s="28">
+      <c r="D44" s="28">
         <v>59.77</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="25">
         <v>43787</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <f t="shared" si="0"/>
         <v>43810</v>
       </c>
-      <c r="C44" s="27">
+      <c r="C45" s="27">
         <v>33.700000000000003</v>
       </c>
-      <c r="D44" s="28">
+      <c r="D45" s="28">
         <v>96.38</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="25">
         <v>43811</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <f t="shared" si="0"/>
         <v>43828</v>
       </c>
-      <c r="C45" s="27">
+      <c r="C46" s="27">
         <v>37.700000000000003</v>
       </c>
-      <c r="D45" s="28">
+      <c r="D46" s="28">
         <v>107.82</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="25">
         <v>43829</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <f t="shared" si="0"/>
         <v>43849</v>
       </c>
-      <c r="C46" s="27">
+      <c r="C47" s="27">
         <v>29.3</v>
       </c>
-      <c r="D46" s="28">
+      <c r="D47" s="28">
         <v>83.8</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="26">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="26">
         <v>43850</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>43881</v>
       </c>
-      <c r="C47" s="27">
+      <c r="C48" s="27">
         <v>37</v>
       </c>
-      <c r="D47" s="28">
+      <c r="D48" s="28">
         <v>105.82</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="19"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="21"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="19"/>
       <c r="B49" s="19"/>
       <c r="C49" s="20"/>
       <c r="D49" s="21"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="19"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
